--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.83333333333333</v>
+        <v>8.747916666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>64.70833293088647</v>
+        <v>10.51510410126905</v>
       </c>
       <c r="E2" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F2" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.57629858220341</v>
+        <v>5.456148519608055</v>
       </c>
       <c r="D3" t="n">
-        <v>3.859691541334706</v>
+        <v>0.6271998754668898</v>
       </c>
       <c r="E3" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F3" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.36446270778363</v>
+        <v>3.309225190014841</v>
       </c>
       <c r="D4" t="n">
-        <v>15.93709524288557</v>
+        <v>2.589777976968906</v>
       </c>
       <c r="E4" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F4" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.70438547663603</v>
+        <v>2.714462639953356</v>
       </c>
       <c r="D5" t="n">
-        <v>14.18994890196616</v>
+        <v>2.305866696569501</v>
       </c>
       <c r="E5" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F5" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.4383633429147</v>
+        <v>5.271234043223639</v>
       </c>
       <c r="D6" t="n">
-        <v>35.71938913441696</v>
+        <v>5.804400734342757</v>
       </c>
       <c r="E6" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F6" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.49447930777076</v>
+        <v>5.605352887512749</v>
       </c>
       <c r="D7" t="n">
-        <v>36.40362435341716</v>
+        <v>5.915588957430289</v>
       </c>
       <c r="E7" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F7" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.403276163364282</v>
+        <v>1.528032376546696</v>
       </c>
       <c r="D8" t="n">
-        <v>7.303367992082693</v>
+        <v>1.186797298713438</v>
       </c>
       <c r="E8" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F8" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.219403307934586</v>
+        <v>1.49815303753937</v>
       </c>
       <c r="D9" t="n">
-        <v>11.12029865669859</v>
+        <v>1.80704853171352</v>
       </c>
       <c r="E9" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F9" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.53661681090037</v>
+        <v>4.799700231771309</v>
       </c>
       <c r="D10" t="n">
-        <v>2.565076418354427</v>
+        <v>0.4168249179825944</v>
       </c>
       <c r="E10" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F10" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.85479049533643</v>
+        <v>5.01390345549217</v>
       </c>
       <c r="D11" t="n">
-        <v>36.67158743107934</v>
+        <v>5.959132957550393</v>
       </c>
       <c r="E11" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F11" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.21964835246783</v>
+        <v>2.473192857276023</v>
       </c>
       <c r="D12" t="n">
-        <v>15.03542854670541</v>
+        <v>2.443257138839629</v>
       </c>
       <c r="E12" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F12" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.36905177483679</v>
+        <v>7.697470913410979</v>
       </c>
       <c r="D13" t="n">
-        <v>30.35353931394012</v>
+        <v>4.93245013851527</v>
       </c>
       <c r="E13" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F13" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>47.43382771675503</v>
+        <v>7.707997003972692</v>
       </c>
       <c r="D14" t="n">
-        <v>49.29580184715787</v>
+        <v>8.010567800163154</v>
       </c>
       <c r="E14" t="n">
-        <v>14.00726929901015</v>
+        <v>2.27618126108915</v>
       </c>
       <c r="F14" t="n">
-        <v>18.25240534678667</v>
+        <v>2.966015868852835</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
